--- a/data/trans_orig/Q4501_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4501_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2007 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32368</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93915</t>
+          <t>93290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130612</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112401</t>
+          <t>112483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155221</t>
+          <t>156999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81035</t>
+          <t>82833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123094</t>
+          <t>120166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164021</t>
+          <t>163544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182942</t>
+          <t>183482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236029</t>
+          <t>236423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152458</t>
+          <t>150182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>198249</t>
+          <t>197703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143326</t>
+          <t>143777</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>186793</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>309074</t>
+          <t>306776</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>371769</t>
+          <t>374105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116500</t>
+          <t>116557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159176</t>
+          <t>157595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59714</t>
+          <t>59831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91023</t>
+          <t>91593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185999</t>
+          <t>185141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238338</t>
+          <t>238466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>269027</t>
+          <t>268109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320148</t>
+          <t>322233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170581</t>
+          <t>168438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216967</t>
+          <t>216557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449621</t>
+          <t>450846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>521596</t>
+          <t>519968</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95455</t>
+          <t>95577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140076</t>
+          <t>137141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>233592</t>
+          <t>235025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292532</t>
+          <t>289788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345047</t>
+          <t>343988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>414032</t>
+          <t>413497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82924</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125177</t>
+          <t>126088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150959</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200092</t>
+          <t>199207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247648</t>
+          <t>248375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311410</t>
+          <t>312882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210747</t>
+          <t>212085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267722</t>
+          <t>267252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>223967</t>
+          <t>224381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279148</t>
+          <t>278752</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>452173</t>
+          <t>453700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>530146</t>
+          <t>529676</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115440</t>
+          <t>117278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>159936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50558</t>
+          <t>50755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81493</t>
+          <t>82616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176426</t>
+          <t>175438</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233273</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337583</t>
+          <t>336519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>404494</t>
+          <t>395832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186024</t>
+          <t>187095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240721</t>
+          <t>239686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>540127</t>
+          <t>537556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>621446</t>
+          <t>621532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113087</t>
+          <t>111756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159576</t>
+          <t>156330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223133</t>
+          <t>222705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>271597</t>
+          <t>272658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350551</t>
+          <t>348822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>417253</t>
+          <t>415149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86322</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124807</t>
+          <t>125517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108332</t>
+          <t>108603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147450</t>
+          <t>148617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203207</t>
+          <t>205690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258121</t>
+          <t>262362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108028</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149501</t>
+          <t>151233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88029</t>
+          <t>89476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125397</t>
+          <t>125292</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>208209</t>
+          <t>204956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>267012</t>
+          <t>264270</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>52080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85896</t>
+          <t>84567</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31871</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56393</t>
+          <t>57469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92919</t>
+          <t>92027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132181</t>
+          <t>134294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215776</t>
+          <t>215320</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>140267</t>
+          <t>140734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184620</t>
+          <t>182586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372590</t>
+          <t>367471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434929</t>
+          <t>439942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145574</t>
+          <t>146237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194846</t>
+          <t>191870</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>284506</t>
+          <t>283893</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>343407</t>
+          <t>340970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>442485</t>
+          <t>443539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>517633</t>
+          <t>518786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>130330</t>
+          <t>133036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174408</t>
+          <t>175302</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>213720</t>
+          <t>214011</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268613</t>
+          <t>270174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>362738</t>
+          <t>358637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>429809</t>
+          <t>430941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199356</t>
+          <t>199417</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249911</t>
+          <t>250038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>180339</t>
+          <t>180468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232810</t>
+          <t>232257</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>390211</t>
+          <t>393209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>464644</t>
+          <t>463443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113583</t>
+          <t>114994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155171</t>
+          <t>156292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69687</t>
+          <t>69364</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>107867</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197220</t>
+          <t>194091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251944</t>
+          <t>250388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>235840</t>
+          <t>235584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>288018</t>
+          <t>288340</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166891</t>
+          <t>167883</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>215267</t>
+          <t>215396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>416635</t>
+          <t>415634</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>490461</t>
+          <t>490609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>402226</t>
+          <t>405320</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>481157</t>
+          <t>483647</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>883648</t>
+          <t>881519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>981531</t>
+          <t>986797</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1311317</t>
+          <t>1312421</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1441957</t>
+          <t>1439413</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>393162</t>
+          <t>388636</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>471170</t>
+          <t>470156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>639424</t>
+          <t>646839</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>737896</t>
+          <t>737946</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1058915</t>
+          <t>1050933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1174740</t>
+          <t>1172299</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>716900</t>
+          <t>720609</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>808679</t>
+          <t>821469</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>679789</t>
+          <t>677653</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>774076</t>
+          <t>773218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1424837</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1560381</t>
+          <t>1559160</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>440639</t>
+          <t>438416</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>521266</t>
+          <t>518153</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>241819</t>
+          <t>241102</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>306752</t>
+          <t>303398</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>699803</t>
+          <t>702190</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>803168</t>
+          <t>803980</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1107115</t>
+          <t>1103399</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1217670</t>
+          <t>1213513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>711480</t>
+          <t>709894</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>808587</t>
+          <t>803922</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1839877</t>
+          <t>1839553</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1991501</t>
+          <t>1990532</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>81027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>88180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127375</t>
+          <t>128359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145675</t>
+          <t>147300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196020</t>
+          <t>195994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55523</t>
+          <t>54621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88039</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>99443</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142538</t>
+          <t>140862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166084</t>
+          <t>167434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216926</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113912</t>
+          <t>112887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154542</t>
+          <t>155805</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156041</t>
+          <t>159652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>204398</t>
+          <t>205457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281330</t>
+          <t>281347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>346751</t>
+          <t>347841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95163</t>
+          <t>93459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136022</t>
+          <t>135646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80842</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152265</t>
+          <t>153475</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203302</t>
+          <t>205097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295943</t>
+          <t>296411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348211</t>
+          <t>349627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197525</t>
+          <t>199751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>249316</t>
+          <t>249646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>507888</t>
+          <t>511012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>584565</t>
+          <t>585911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98326</t>
+          <t>99542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141762</t>
+          <t>143585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209370</t>
+          <t>211384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268833</t>
+          <t>267503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>322814</t>
+          <t>324620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394736</t>
+          <t>394931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80904</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120618</t>
+          <t>118021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168998</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>221522</t>
+          <t>220570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263376</t>
+          <t>258944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329031</t>
+          <t>326614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>182782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>234990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>218860</t>
+          <t>218591</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>273146</t>
+          <t>274861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>420053</t>
+          <t>417598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>496924</t>
+          <t>495550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111406</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155218</t>
+          <t>157804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64919</t>
+          <t>62655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101113</t>
+          <t>98931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184679</t>
+          <t>185620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241435</t>
+          <t>242683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422636</t>
+          <t>425423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488146</t>
+          <t>488583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246488</t>
+          <t>242873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303997</t>
+          <t>304417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>686445</t>
+          <t>681792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>775883</t>
+          <t>776618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62322</t>
+          <t>60417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96640</t>
+          <t>97780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163394</t>
+          <t>164353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>212158</t>
+          <t>214325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233258</t>
+          <t>235088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299382</t>
+          <t>296621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69078</t>
+          <t>69570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106311</t>
+          <t>105492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91208</t>
+          <t>91127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131481</t>
+          <t>131063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167074</t>
+          <t>170746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224490</t>
+          <t>226133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173968</t>
+          <t>176729</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224880</t>
+          <t>227750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>167639</t>
+          <t>166335</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216995</t>
+          <t>215861</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356349</t>
+          <t>357500</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>428097</t>
+          <t>425232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58543</t>
+          <t>59562</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91808</t>
+          <t>93235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54313</t>
+          <t>53338</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86012</t>
+          <t>85329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124394</t>
+          <t>122486</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168856</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290009</t>
+          <t>291311</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>346905</t>
+          <t>348618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191102</t>
+          <t>191976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245356</t>
+          <t>243289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>496952</t>
+          <t>501066</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>576818</t>
+          <t>576446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86226</t>
+          <t>87063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125733</t>
+          <t>125847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>236656</t>
+          <t>235604</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>293695</t>
+          <t>291353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336144</t>
+          <t>338403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408150</t>
+          <t>408003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107045</t>
+          <t>106409</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149747</t>
+          <t>148867</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167492</t>
+          <t>165838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216949</t>
+          <t>215081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>284507</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>346725</t>
+          <t>350659</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>200134</t>
+          <t>202281</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>253570</t>
+          <t>252451</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>198935</t>
+          <t>199175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>253821</t>
+          <t>254348</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>413933</t>
+          <t>417475</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>493618</t>
+          <t>491527</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100230</t>
+          <t>100734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143075</t>
+          <t>141853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80551</t>
+          <t>80414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122206</t>
+          <t>119175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>190818</t>
+          <t>188165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>247693</t>
+          <t>248412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339280</t>
+          <t>338235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>404627</t>
+          <t>401648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>239318</t>
+          <t>240450</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>299842</t>
+          <t>299620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>600170</t>
+          <t>595077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>687040</t>
+          <t>683713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>330552</t>
+          <t>330966</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>404061</t>
+          <t>407968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>745931</t>
+          <t>741312</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>854032</t>
+          <t>842992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1097213</t>
+          <t>1089078</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1225524</t>
+          <t>1221873</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>343413</t>
+          <t>339621</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>418714</t>
+          <t>416772</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>569648</t>
+          <t>570066</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>663897</t>
+          <t>661281</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>927069</t>
+          <t>932688</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1059102</t>
+          <t>1059617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>721961</t>
+          <t>720037</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>821886</t>
+          <t>817169</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>791637</t>
+          <t>791147</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>896956</t>
+          <t>897865</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1540790</t>
+          <t>1538712</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1688826</t>
+          <t>1684756</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>396709</t>
+          <t>402215</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>477826</t>
+          <t>483975</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>274629</t>
+          <t>276311</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>345785</t>
+          <t>344095</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>697506</t>
+          <t>697310</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>807294</t>
+          <t>803408</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1408486</t>
+          <t>1405382</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1529717</t>
+          <t>1520278</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>929597</t>
+          <t>932785</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1038300</t>
+          <t>1040360</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2363567</t>
+          <t>2373724</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2531910</t>
+          <t>2536116</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58037</t>
+          <t>59308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63074</t>
+          <t>62317</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95089</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100704</t>
+          <t>101440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141620</t>
+          <t>142807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86599</t>
+          <t>86270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125386</t>
+          <t>126364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145916</t>
+          <t>144675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191159</t>
+          <t>189743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243911</t>
+          <t>244251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302467</t>
+          <t>302358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118725</t>
+          <t>119811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161142</t>
+          <t>162878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125683</t>
+          <t>127188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167588</t>
+          <t>167450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253611</t>
+          <t>256141</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>318263</t>
+          <t>312502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58829</t>
+          <t>58178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91613</t>
+          <t>89039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>43071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70338</t>
+          <t>71231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107052</t>
+          <t>109005</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150473</t>
+          <t>149652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288196</t>
+          <t>287410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337956</t>
+          <t>343201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202934</t>
+          <t>201140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250865</t>
+          <t>251745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506366</t>
+          <t>504210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>578713</t>
+          <t>575668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>79388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120593</t>
+          <t>119390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158684</t>
+          <t>157295</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210668</t>
+          <t>209236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248806</t>
+          <t>249634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315201</t>
+          <t>314665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208841</t>
+          <t>210132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262439</t>
+          <t>264650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294451</t>
+          <t>293500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>352984</t>
+          <t>353714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>514568</t>
+          <t>518711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>598827</t>
+          <t>603394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>200331</t>
+          <t>201712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255020</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199525</t>
+          <t>199867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>253996</t>
+          <t>252415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>416270</t>
+          <t>415025</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>490813</t>
+          <t>494509</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71793</t>
+          <t>71992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>109037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39566</t>
+          <t>41011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69159</t>
+          <t>70763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118958</t>
+          <t>119699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169530</t>
+          <t>166345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331893</t>
+          <t>336597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>396229</t>
+          <t>401846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230943</t>
+          <t>228386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290550</t>
+          <t>290593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582359</t>
+          <t>582923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666562</t>
+          <t>670887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62891</t>
+          <t>58215</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>98691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121283</t>
+          <t>123938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164827</t>
+          <t>166451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193813</t>
+          <t>195430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249719</t>
+          <t>251688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194982</t>
+          <t>194212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245180</t>
+          <t>246733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255789</t>
+          <t>256872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313738</t>
+          <t>310243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>464679</t>
+          <t>462180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>539844</t>
+          <t>536329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153027</t>
+          <t>155281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199519</t>
+          <t>201300</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128322</t>
+          <t>126629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171456</t>
+          <t>173641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>291536</t>
+          <t>293611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>360950</t>
+          <t>361445</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45670</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77088</t>
+          <t>76991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28466</t>
+          <t>29253</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80984</t>
+          <t>81278</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119983</t>
+          <t>120705</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192956</t>
+          <t>195485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246131</t>
+          <t>246816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143492</t>
+          <t>139703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188337</t>
+          <t>189253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349072</t>
+          <t>349374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422443</t>
+          <t>418935</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110213</t>
+          <t>106989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153718</t>
+          <t>150353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202142</t>
+          <t>199819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256281</t>
+          <t>256625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>319207</t>
+          <t>320992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>388435</t>
+          <t>390974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>159979</t>
+          <t>159660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206970</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>224649</t>
+          <t>226042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>281945</t>
+          <t>285000</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>400883</t>
+          <t>401602</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>476037</t>
+          <t>478083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187797</t>
+          <t>187612</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237732</t>
+          <t>239425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>192347</t>
+          <t>191365</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246926</t>
+          <t>246337</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>395510</t>
+          <t>394025</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>469075</t>
+          <t>467839</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73675</t>
+          <t>73225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>40885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69975</t>
+          <t>71174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93780</t>
+          <t>93555</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>134774</t>
+          <t>133382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>325963</t>
+          <t>323936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>385991</t>
+          <t>385431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>260006</t>
+          <t>257688</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320927</t>
+          <t>320762</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>600381</t>
+          <t>601546</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>687335</t>
+          <t>691042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>313889</t>
+          <t>312979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>386145</t>
+          <t>387565</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>582410</t>
+          <t>579298</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>678039</t>
+          <t>675891</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>923176</t>
+          <t>917960</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1036768</t>
+          <t>1038293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>693273</t>
+          <t>693368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>796185</t>
+          <t>789621</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>971379</t>
+          <t>977402</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1082766</t>
+          <t>1082335</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1689626</t>
+          <t>1697688</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1846998</t>
+          <t>1840316</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>707497</t>
+          <t>702853</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>804746</t>
+          <t>802181</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>692124</t>
+          <t>689353</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>789127</t>
+          <t>787824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1424737</t>
+          <t>1424980</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1560807</t>
+          <t>1561632</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>248764</t>
+          <t>247292</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>315665</t>
+          <t>311492</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>176287</t>
+          <t>175940</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>231001</t>
+          <t>233309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>433404</t>
+          <t>437379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>523059</t>
+          <t>527512</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1197366</t>
+          <t>1200147</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1314389</t>
+          <t>1314108</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>882901</t>
+          <t>883446</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>994509</t>
+          <t>989534</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2112501</t>
+          <t>2108780</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2272910</t>
+          <t>2274481</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4501_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4501_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14255</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>93950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132279</t>
+          <t>131636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112483</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156999</t>
+          <t>156605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82833</t>
+          <t>83545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120166</t>
+          <t>122716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163544</t>
+          <t>166230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183482</t>
+          <t>183124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236423</t>
+          <t>236752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150182</t>
+          <t>151779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>197703</t>
+          <t>197868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143777</t>
+          <t>143490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186793</t>
+          <t>187390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>306776</t>
+          <t>308552</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>374105</t>
+          <t>371214</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116557</t>
+          <t>116711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157595</t>
+          <t>160575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59831</t>
+          <t>59531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91593</t>
+          <t>92043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185141</t>
+          <t>187237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238466</t>
+          <t>238604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268109</t>
+          <t>266552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322233</t>
+          <t>318650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168438</t>
+          <t>171206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216557</t>
+          <t>217103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450846</t>
+          <t>451749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>519968</t>
+          <t>522968</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95577</t>
+          <t>95551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137141</t>
+          <t>137841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>235025</t>
+          <t>235964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289788</t>
+          <t>293715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>343988</t>
+          <t>342452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413497</t>
+          <t>417471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>86846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126088</t>
+          <t>125904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>150911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199207</t>
+          <t>200898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248375</t>
+          <t>246211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312882</t>
+          <t>312999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>212085</t>
+          <t>213168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267252</t>
+          <t>267998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278752</t>
+          <t>277463</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453700</t>
+          <t>453085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>529676</t>
+          <t>528133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117278</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159936</t>
+          <t>161186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>50150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82616</t>
+          <t>82869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175438</t>
+          <t>178288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>233146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336519</t>
+          <t>334510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>395832</t>
+          <t>395477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187095</t>
+          <t>185451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>239686</t>
+          <t>239349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>537556</t>
+          <t>535884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>621532</t>
+          <t>621031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111756</t>
+          <t>113017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156330</t>
+          <t>158014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>222705</t>
+          <t>225409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>272658</t>
+          <t>274154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348822</t>
+          <t>349079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415149</t>
+          <t>415809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88281</t>
+          <t>88050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125517</t>
+          <t>126828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,47 +2224,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>18,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>126644</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106683</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>148161</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>18,52%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126644</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>108603</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148617</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205690</t>
+          <t>203452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262362</t>
+          <t>260553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110578</t>
+          <t>108279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151233</t>
+          <t>149970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89476</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125292</t>
+          <t>125783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>204956</t>
+          <t>207289</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>264270</t>
+          <t>263253</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52080</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84567</t>
+          <t>86210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57469</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92027</t>
+          <t>88255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>132607</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215320</t>
+          <t>213313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267675</t>
+          <t>264510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>140734</t>
+          <t>140422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182586</t>
+          <t>184404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367471</t>
+          <t>370015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>439942</t>
+          <t>437277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146237</t>
+          <t>148510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191870</t>
+          <t>194246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>283893</t>
+          <t>283646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>340970</t>
+          <t>344929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443539</t>
+          <t>441731</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>518786</t>
+          <t>518980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>133036</t>
+          <t>131977</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175302</t>
+          <t>175775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>214011</t>
+          <t>214064</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>270174</t>
+          <t>269092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>358637</t>
+          <t>361237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>430941</t>
+          <t>428545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199417</t>
+          <t>199388</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250038</t>
+          <t>251209</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>180468</t>
+          <t>180760</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232257</t>
+          <t>234199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>393209</t>
+          <t>393465</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>463443</t>
+          <t>468007</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114994</t>
+          <t>114231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156292</t>
+          <t>155338</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69364</t>
+          <t>70643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107867</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194091</t>
+          <t>193832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>250388</t>
+          <t>250782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>235584</t>
+          <t>237055</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>288340</t>
+          <t>290260</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167883</t>
+          <t>166509</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>215396</t>
+          <t>216402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>415634</t>
+          <t>415932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>490609</t>
+          <t>494155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>405320</t>
+          <t>403778</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>483647</t>
+          <t>483688</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>881519</t>
+          <t>882901</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>986797</t>
+          <t>987585</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1312421</t>
+          <t>1308222</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1439413</t>
+          <t>1442146</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>388636</t>
+          <t>390318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>470156</t>
+          <t>465146</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>646839</t>
+          <t>643551</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>737946</t>
+          <t>735123</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1050933</t>
+          <t>1053344</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1172299</t>
+          <t>1173248</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>720609</t>
+          <t>714891</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>821469</t>
+          <t>810884</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>677653</t>
+          <t>675193</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>773218</t>
+          <t>772620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1424837</t>
+          <t>1425428</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1559160</t>
+          <t>1559737</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>438416</t>
+          <t>438473</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>518153</t>
+          <t>518267</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>241102</t>
+          <t>240472</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>303398</t>
+          <t>304992</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>702190</t>
+          <t>695857</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>803980</t>
+          <t>801297</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1103399</t>
+          <t>1107958</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1213513</t>
+          <t>1218354</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>709894</t>
+          <t>711978</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>803922</t>
+          <t>806871</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1839553</t>
+          <t>1839698</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1990532</t>
+          <t>1995825</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49269</t>
+          <t>49557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81027</t>
+          <t>79556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88180</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128359</t>
+          <t>127189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147300</t>
+          <t>144841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>194199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>89767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99443</t>
+          <t>103162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140862</t>
+          <t>141745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167434</t>
+          <t>164847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>219307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112887</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155805</t>
+          <t>154657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159652</t>
+          <t>157580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205457</t>
+          <t>204553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281347</t>
+          <t>282296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>347841</t>
+          <t>346221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93459</t>
+          <t>93805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135646</t>
+          <t>134271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50016</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82530</t>
+          <t>81394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153475</t>
+          <t>154200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205097</t>
+          <t>205786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>296411</t>
+          <t>297977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349627</t>
+          <t>350734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199751</t>
+          <t>200175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>249646</t>
+          <t>248931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511012</t>
+          <t>508432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>585911</t>
+          <t>582678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99542</t>
+          <t>99058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143585</t>
+          <t>144565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211384</t>
+          <t>210018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267503</t>
+          <t>265806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>324620</t>
+          <t>326420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394931</t>
+          <t>396479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>80102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118021</t>
+          <t>120047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170310</t>
+          <t>167078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220570</t>
+          <t>221572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258944</t>
+          <t>261866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326614</t>
+          <t>328403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182782</t>
+          <t>181351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>234990</t>
+          <t>238196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>218591</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>274861</t>
+          <t>273258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>417598</t>
+          <t>415962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>495550</t>
+          <t>495697</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111573</t>
+          <t>111936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157804</t>
+          <t>156932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>61906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98931</t>
+          <t>96842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185620</t>
+          <t>184863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242683</t>
+          <t>241304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425423</t>
+          <t>419527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488583</t>
+          <t>486321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242873</t>
+          <t>244264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304417</t>
+          <t>301172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681792</t>
+          <t>682810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>776618</t>
+          <t>774063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60417</t>
+          <t>61627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97780</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164353</t>
+          <t>162938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214325</t>
+          <t>212336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235088</t>
+          <t>234384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296621</t>
+          <t>297287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>67405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105492</t>
+          <t>105045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91127</t>
+          <t>90605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131063</t>
+          <t>130437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170746</t>
+          <t>169806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226133</t>
+          <t>223381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176729</t>
+          <t>176293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227750</t>
+          <t>227450</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166335</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>215861</t>
+          <t>215151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357500</t>
+          <t>354893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>425232</t>
+          <t>429604</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>93818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53338</t>
+          <t>56214</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>88906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122486</t>
+          <t>122055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169149</t>
+          <t>169506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291311</t>
+          <t>291152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>348618</t>
+          <t>349227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191976</t>
+          <t>193078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243289</t>
+          <t>246815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501066</t>
+          <t>500940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>576446</t>
+          <t>578186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87063</t>
+          <t>84729</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>126209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235604</t>
+          <t>235789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291353</t>
+          <t>292131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>338403</t>
+          <t>336467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408003</t>
+          <t>402330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106409</t>
+          <t>104250</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148867</t>
+          <t>147714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,82 +6548,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>15,59%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>190116</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>164730</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>216103</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>15,71%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>190116</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>165838</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>215081</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>315673</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>284682</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>350731</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>20,51%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>315673</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>282110</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>350659</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202281</t>
+          <t>201258</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>252451</t>
+          <t>252583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>199175</t>
+          <t>202568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>254348</t>
+          <t>256965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>417475</t>
+          <t>416210</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>491527</t>
+          <t>492583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100734</t>
+          <t>101675</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141853</t>
+          <t>142421</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80414</t>
+          <t>80721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119175</t>
+          <t>119292</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>188165</t>
+          <t>191790</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>248412</t>
+          <t>250116</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>338235</t>
+          <t>341087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>401648</t>
+          <t>403623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>299620</t>
+          <t>297397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>595077</t>
+          <t>596038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>683713</t>
+          <t>680174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>330966</t>
+          <t>327596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>407968</t>
+          <t>404469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>741312</t>
+          <t>737077</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>842992</t>
+          <t>843823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1089078</t>
+          <t>1100705</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1221873</t>
+          <t>1224263</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>339621</t>
+          <t>343830</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>416772</t>
+          <t>421027</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>570066</t>
+          <t>566930</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>661281</t>
+          <t>662265</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>932688</t>
+          <t>932674</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1059617</t>
+          <t>1062139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>720037</t>
+          <t>723631</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>817169</t>
+          <t>824980</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>791147</t>
+          <t>794558</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>897865</t>
+          <t>898265</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1538712</t>
+          <t>1540471</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1684756</t>
+          <t>1688292</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>402215</t>
+          <t>400241</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>483975</t>
+          <t>482973</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>276311</t>
+          <t>276119</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>344095</t>
+          <t>342944</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>697310</t>
+          <t>706902</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>803408</t>
+          <t>809484</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1405382</t>
+          <t>1407171</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1520278</t>
+          <t>1531173</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>932785</t>
+          <t>929445</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1040360</t>
+          <t>1039949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2373724</t>
+          <t>2353967</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2536116</t>
+          <t>2527963</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59308</t>
+          <t>57594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62317</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>96733</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101440</t>
+          <t>101659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142807</t>
+          <t>143160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>87142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126364</t>
+          <t>124947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144675</t>
+          <t>145988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189743</t>
+          <t>189210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244251</t>
+          <t>243920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302358</t>
+          <t>301087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119811</t>
+          <t>119193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162878</t>
+          <t>160414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127188</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167450</t>
+          <t>167236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256141</t>
+          <t>254200</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>312502</t>
+          <t>314191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58178</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89039</t>
+          <t>90950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71231</t>
+          <t>70666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109005</t>
+          <t>109060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149652</t>
+          <t>151511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287410</t>
+          <t>288425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>343201</t>
+          <t>340816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201140</t>
+          <t>199453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251745</t>
+          <t>248382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504210</t>
+          <t>505814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>575668</t>
+          <t>577960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79388</t>
+          <t>78962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119390</t>
+          <t>119125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157295</t>
+          <t>158999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209236</t>
+          <t>207868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249634</t>
+          <t>247801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314665</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210132</t>
+          <t>210284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264650</t>
+          <t>266368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293500</t>
+          <t>292484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353714</t>
+          <t>353235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>518711</t>
+          <t>517783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>603394</t>
+          <t>598283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201712</t>
+          <t>199208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>254114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199867</t>
+          <t>197020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>252415</t>
+          <t>250429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>415025</t>
+          <t>415129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>494509</t>
+          <t>495557</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71992</t>
+          <t>71147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109037</t>
+          <t>108002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41011</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70763</t>
+          <t>70548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119699</t>
+          <t>118929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>165828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336597</t>
+          <t>335257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>401846</t>
+          <t>399466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228386</t>
+          <t>231803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290593</t>
+          <t>288691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582923</t>
+          <t>581871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>670887</t>
+          <t>667383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58215</t>
+          <t>62146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98691</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>121933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166451</t>
+          <t>167847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>195430</t>
+          <t>195766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251688</t>
+          <t>253949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194212</t>
+          <t>193339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246733</t>
+          <t>247165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256872</t>
+          <t>254895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310243</t>
+          <t>311674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>462180</t>
+          <t>468036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>536329</t>
+          <t>539839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155281</t>
+          <t>152287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201300</t>
+          <t>199084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126629</t>
+          <t>127787</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>173641</t>
+          <t>173523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293611</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>361445</t>
+          <t>355826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46769</t>
+          <t>44461</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76991</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53791</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81278</t>
+          <t>81176</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120705</t>
+          <t>122838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195485</t>
+          <t>193495</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246816</t>
+          <t>245965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139703</t>
+          <t>142058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189253</t>
+          <t>189327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349374</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418935</t>
+          <t>417653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>106950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>150353</t>
+          <t>153002</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199819</t>
+          <t>200326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256625</t>
+          <t>255036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320992</t>
+          <t>319841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390974</t>
+          <t>389316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>159660</t>
+          <t>159337</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208474</t>
+          <t>209246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>226042</t>
+          <t>226272</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285000</t>
+          <t>283519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>401602</t>
+          <t>402029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>478083</t>
+          <t>475054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>187612</t>
+          <t>190322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>239425</t>
+          <t>240160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191365</t>
+          <t>192170</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246337</t>
+          <t>244720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>394025</t>
+          <t>393741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>467839</t>
+          <t>464678</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73225</t>
+          <t>73750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71174</t>
+          <t>71765</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93555</t>
+          <t>92546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133382</t>
+          <t>133381</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323936</t>
+          <t>323727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>385431</t>
+          <t>382279</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>257688</t>
+          <t>260186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320762</t>
+          <t>323737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>601546</t>
+          <t>602250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>691042</t>
+          <t>686868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>312979</t>
+          <t>310682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>387565</t>
+          <t>385995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>579298</t>
+          <t>581647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>675891</t>
+          <t>674510</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>917960</t>
+          <t>913117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1038293</t>
+          <t>1037346</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>693368</t>
+          <t>697777</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>789621</t>
+          <t>793391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>977402</t>
+          <t>975979</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1082335</t>
+          <t>1089741</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1697688</t>
+          <t>1699987</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1840316</t>
+          <t>1840821</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>702853</t>
+          <t>709308</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>802181</t>
+          <t>804765</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>689353</t>
+          <t>683691</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>787824</t>
+          <t>787774</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1424980</t>
+          <t>1423439</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1561632</t>
+          <t>1568325</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>247292</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>311492</t>
+          <t>312760</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>175940</t>
+          <t>178024</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>233309</t>
+          <t>234029</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>437379</t>
+          <t>434825</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>527512</t>
+          <t>523628</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1200147</t>
+          <t>1190529</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1314108</t>
+          <t>1312610</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>883446</t>
+          <t>881385</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>989534</t>
+          <t>997123</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2108780</t>
+          <t>2116472</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2274481</t>
+          <t>2268993</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
